--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55849\Desktop\Automacoes_SIPAC\02_Indicador _Atrasos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Unidade</t>
   </si>
@@ -81,10 +76,10 @@
     <t>ALMOXARIFADO DO HOSPITAL REGIONAL CLEODON CARLOS DE ANDRADE (20.00.17.01)</t>
   </si>
   <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL DEOCLÉCIO MARQUES (20.00.07.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL DEOCLÉCIO MARQUES (20.00.07.01)</t>
+    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUT/HRDML (20.00.07.11.01.98)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO COMUM - ALMX/HRDML (20.00.07.11.01.99)</t>
   </si>
   <si>
     <t>ALMOXARIFADO DO HOSPITAL GISELDA TRIGUEIRO - ALMX/HGT/SESAP (20.00.03.01)</t>
@@ -141,65 +136,62 @@
     <t>ALMOXARIFADO DO HOSPITAL REGIONAL MONSENHOR EXPEDITO (20.00.11.01)</t>
   </si>
   <si>
-    <t>Unidade Posição 38</t>
-  </si>
-  <si>
-    <t>Unidade Posição 39</t>
-  </si>
-  <si>
-    <t>Unidade Posição 40</t>
-  </si>
-  <si>
-    <t>Unidade Posição 41</t>
-  </si>
-  <si>
-    <t>Unidade Posição 42</t>
-  </si>
-  <si>
-    <t>Unidade Posição 43</t>
-  </si>
-  <si>
-    <t>Unidade Posição 44</t>
-  </si>
-  <si>
-    <t>Unidade Posição 45</t>
-  </si>
-  <si>
-    <t>Unidade Posição 46</t>
-  </si>
-  <si>
-    <t>Unidade Posição 47</t>
-  </si>
-  <si>
-    <t>Unidade Posição 48</t>
-  </si>
-  <si>
-    <t>Unidade Posição 49</t>
-  </si>
-  <si>
-    <t>Unidade Posição 50</t>
-  </si>
-  <si>
-    <t>Unidade Posição 51</t>
-  </si>
-  <si>
-    <t>Unidade Posição 52</t>
-  </si>
-  <si>
-    <t>Unidade Posição 53</t>
-  </si>
-  <si>
-    <t>Unidade Posição 54</t>
-  </si>
-  <si>
-    <t>Unidade Posição 55</t>
+    <t>ALMOXARIFADO DO HOSPITAL DA MULHER PARTEIRA MARIA CORREIA (20.00.45.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL DA MULHER PARTEIRA MARIA CORREIA (20.00.45.03)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL NELSON INÁCIO DOS SANTOS (20.00.12.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL NELSON INÁCIO DOS SANTOS (20.00.12.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL DOUTOR RAFAEL FERNANDES (20.00.14.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL REGIONAL DOUTOR RAFAEL FERNANDES (20.00.14.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL TARCÍSIO MAIA (20.00.13.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL TARCÍSIO MAIA (20.00.13.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL ESTADUAL TELECILA FREITAS FONTES (20.00.19.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL ESTADUAL TELECILA FREITAS FONTES (20.00.19.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL MONSENHOR WALFREDO GURGEL - ALMX/HMWG (20.00.01.01.04.03.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUT/HMWG (20.00.01.01.05.06.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO LABORATÓRIO DE CITOPATOLOGIA DE MOSSORÓ (20.99.10.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DE SUPRIMENTOS DO LACEN - ALMX/LACEN/SES (20.00.20.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO LAREM (20.00.22.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO LABORATÓRIO REGIONAL DE CAICÓ DR. JOÃO PAULO FILGUEIRA (20.00.21.03)</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE ALMOXARIFADO - DIVALMX/LAREPF/SESAP (20.00.23.01.01.02)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,19 +254,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -316,7 +300,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -348,10 +332,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -383,7 +366,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -559,16 +541,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="64.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,18 +556,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C2">
-        <v>28893</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>36581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -601,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -612,18 +589,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="C5">
-        <v>76478</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -634,18 +611,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C7">
-        <v>35217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45808</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -653,43 +630,43 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>38701</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C11">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -697,32 +674,32 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="C14">
-        <v>561701</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>615060</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -733,18 +710,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -755,40 +732,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>13676</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14980</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -799,29 +776,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C22">
-        <v>23384</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26464</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -832,7 +809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -843,29 +820,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="C26">
-        <v>763496</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>836891</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -876,7 +853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -887,62 +864,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>10927</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14579</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C34">
-        <v>65353</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71862</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -953,18 +930,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -972,21 +949,21 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -997,40 +974,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1041,40 +1018,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>449727</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1085,18 +1062,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1107,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1118,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1129,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1140,29 +1117,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+        <v>36963</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1170,17 +1147,6 @@
         <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
         <v>0</v>
       </c>
     </row>

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -564,7 +564,7 @@
         <v>105</v>
       </c>
       <c r="C2">
-        <v>36581</v>
+        <v>36686</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -594,10 +594,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C5">
-        <v>99567</v>
+        <v>99893</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -616,10 +616,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C7">
-        <v>45808</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -627,10 +627,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>41331</v>
+        <v>41366</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -649,10 +649,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -663,7 +663,7 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>1312</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4482</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -696,7 +696,7 @@
         <v>707</v>
       </c>
       <c r="C14">
-        <v>615060</v>
+        <v>615767</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -740,7 +740,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -751,7 +751,7 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>14980</v>
+        <v>14998</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>26464</v>
+        <v>26506</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -828,7 +828,7 @@
         <v>978</v>
       </c>
       <c r="C26">
-        <v>836891</v>
+        <v>837869</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -836,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>257</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -883,7 +883,7 @@
         <v>52</v>
       </c>
       <c r="C31">
-        <v>14579</v>
+        <v>14631</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,7 +894,7 @@
         <v>13</v>
       </c>
       <c r="C32">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -916,7 +916,7 @@
         <v>88</v>
       </c>
       <c r="C34">
-        <v>71862</v>
+        <v>71950</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1901</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -957,10 +957,10 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -982,7 +982,7 @@
         <v>90</v>
       </c>
       <c r="C40">
-        <v>2616</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -990,10 +990,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1026,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="C44">
-        <v>2171</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1037,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1048,7 +1048,7 @@
         <v>397</v>
       </c>
       <c r="C46">
-        <v>449727</v>
+        <v>450124</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>116</v>
       </c>
       <c r="C53">
-        <v>36963</v>
+        <v>37079</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Unidade</t>
   </si>
@@ -31,160 +31,163 @@
     <t>ALMOXARIFADO DA COORDENADORIA DE REGULAÇÃO EM SAÚDE E AVALIAÇÃO - ALMX/SESAP (20.11.52.99)</t>
   </si>
   <si>
-    <t>ALMOXARIFADO DO CENTRO ESTADUAL DE REABILITAÇÃO E ATENÇÃO AMBULATORIAL ESPECIALIZADA - ALMX/CERAE/SES (20.00.25.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO CERAE (20.00.25.10)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HEMOCENTRO DE CAICÓ (20.00.27.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO COLETA E TRANSFUSÃO DO HEMOCENTRO DE PAU DOS FERROS - ALMX/CT/HEM/PF (20.00.30.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HEMOCENTRO DALTON CUNHA - ALMX/HEM/NAT/SESAP (20.00.26.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HEMOCENTRO DALTON CUNHA - ALMX/HEM/NUT/SESAP (20.00.26.40)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HEMOCENTRO DE MOSSORÓ (20.00.28.13)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL AGUINALDO PEREIRA (20.00.16.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL AGUINALDO PEREIRA (20.00.16.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL ALFREDO MESQUITA FILHO - ALMX/HRAMF (20.00.06.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL ALFREDO MESQUITA FILHO - ALMX/NUTHRAMF (20.00.06.98)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL REGIONAL ANTÔNIO BARROS (20.00.08.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL MONSENHOR ANTÔNIO BARROS (20.00.08.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL CLEODON CARLOS DE ANDRADE (20.00.17.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL CLEODON CARLOS DE ANDRADE (20.00.17.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUT/HRDML (20.00.07.11.01.98)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO COMUM - ALMX/HRDML (20.00.07.11.01.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL GISELDA TRIGUEIRO - ALMX/HGT/SESAP (20.00.03.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL GISELDA TRIGUEIRO (20.00.03.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL HÉLIO MORAIS MARINHO (20.00.15.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL HÉLIO MORAIS MARINHO (20.00.15.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL GERAL DOUTOR JOÃO MACHADO (20.00.04.40)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL GERAL DOUTOR JOÃO MACHADO (20.00.04.43)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL JOSEFA ALVES GODEIRO (20.00.10.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL JOSEFA ALVES GODEIRO (20.00.10.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HJPB - ALMX/NUTR/HJPB (20.00.02.98)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO - ALMX/HJPB (20.00.02.01.01.02.01.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL LINDOLFO GOMES VIDAL (20.00.09.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL LINDOLFO GOMES VIDAL (20.00.09.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL MARIA ALICE FERNANDES (20.00.05.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL MARIA ALICE FERNANDES (20.00.05.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO - ALMX/HRMC (20.00.18.12.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUTR/HRMC (20.00.18.11.03.02.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL MONSENHOR EXPEDITO (20.00.11.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL MONSENHOR EXPEDITO (20.00.11.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL DA MULHER PARTEIRA MARIA CORREIA (20.00.45.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL DA MULHER PARTEIRA MARIA CORREIA (20.00.45.03)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL NELSON INÁCIO DOS SANTOS (20.00.12.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL NELSON INÁCIO DOS SANTOS (20.00.12.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL REGIONAL DOUTOR RAFAEL FERNANDES (20.00.14.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL REGIONAL DOUTOR RAFAEL FERNANDES (20.00.14.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL TARCÍSIO MAIA (20.00.13.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL TARCÍSIO MAIA (20.00.13.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL ESTADUAL TELECILA FREITAS FONTES (20.00.19.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL ESTADUAL TELECILA FREITAS FONTES (20.00.19.02)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO HOSPITAL MONSENHOR WALFREDO GURGEL - ALMX/HMWG (20.00.01.01.04.03.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUT/HMWG (20.00.01.01.05.06.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DO LABORATÓRIO DE CITOPATOLOGIA DE MOSSORÓ (20.99.10.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO DE SUPRIMENTOS DO LACEN - ALMX/LACEN/SES (20.00.20.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO LAREM (20.00.22.01)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO LABORATÓRIO REGIONAL DE CAICÓ DR. JOÃO PAULO FILGUEIRA (20.00.21.03)</t>
-  </si>
-  <si>
-    <t>DIVISÃO DE ALMOXARIFADO - DIVALMX/LAREPF/SESAP (20.00.23.01.01.02)</t>
+    <t>Unidade Posição 3</t>
+  </si>
+  <si>
+    <t>Unidade Posição 4</t>
+  </si>
+  <si>
+    <t>Unidade Posição 5</t>
+  </si>
+  <si>
+    <t>Unidade Posição 6</t>
+  </si>
+  <si>
+    <t>Unidade Posição 7</t>
+  </si>
+  <si>
+    <t>Unidade Posição 8</t>
+  </si>
+  <si>
+    <t>Unidade Posição 9</t>
+  </si>
+  <si>
+    <t>Unidade Posição 10</t>
+  </si>
+  <si>
+    <t>Unidade Posição 11</t>
+  </si>
+  <si>
+    <t>Unidade Posição 12</t>
+  </si>
+  <si>
+    <t>Unidade Posição 13</t>
+  </si>
+  <si>
+    <t>Unidade Posição 14</t>
+  </si>
+  <si>
+    <t>Unidade Posição 15</t>
+  </si>
+  <si>
+    <t>Unidade Posição 16</t>
+  </si>
+  <si>
+    <t>Unidade Posição 17</t>
+  </si>
+  <si>
+    <t>Unidade Posição 18</t>
+  </si>
+  <si>
+    <t>Unidade Posição 19</t>
+  </si>
+  <si>
+    <t>Unidade Posição 20</t>
+  </si>
+  <si>
+    <t>Unidade Posição 21</t>
+  </si>
+  <si>
+    <t>Unidade Posição 22</t>
+  </si>
+  <si>
+    <t>Unidade Posição 23</t>
+  </si>
+  <si>
+    <t>Unidade Posição 24</t>
+  </si>
+  <si>
+    <t>Unidade Posição 25</t>
+  </si>
+  <si>
+    <t>Unidade Posição 26</t>
+  </si>
+  <si>
+    <t>Unidade Posição 27</t>
+  </si>
+  <si>
+    <t>Unidade Posição 28</t>
+  </si>
+  <si>
+    <t>Unidade Posição 29</t>
+  </si>
+  <si>
+    <t>Unidade Posição 30</t>
+  </si>
+  <si>
+    <t>Unidade Posição 31</t>
+  </si>
+  <si>
+    <t>Unidade Posição 32</t>
+  </si>
+  <si>
+    <t>Unidade Posição 33</t>
+  </si>
+  <si>
+    <t>Unidade Posição 34</t>
+  </si>
+  <si>
+    <t>Unidade Posição 35</t>
+  </si>
+  <si>
+    <t>Unidade Posição 36</t>
+  </si>
+  <si>
+    <t>Unidade Posição 37</t>
+  </si>
+  <si>
+    <t>Unidade Posição 38</t>
+  </si>
+  <si>
+    <t>Unidade Posição 39</t>
+  </si>
+  <si>
+    <t>Unidade Posição 40</t>
+  </si>
+  <si>
+    <t>Unidade Posição 41</t>
+  </si>
+  <si>
+    <t>Unidade Posição 42</t>
+  </si>
+  <si>
+    <t>Unidade Posição 43</t>
+  </si>
+  <si>
+    <t>Unidade Posição 44</t>
+  </si>
+  <si>
+    <t>Unidade Posição 45</t>
+  </si>
+  <si>
+    <t>Unidade Posição 46</t>
+  </si>
+  <si>
+    <t>Unidade Posição 47</t>
+  </si>
+  <si>
+    <t>Unidade Posição 48</t>
+  </si>
+  <si>
+    <t>Unidade Posição 49</t>
+  </si>
+  <si>
+    <t>Unidade Posição 50</t>
+  </si>
+  <si>
+    <t>Unidade Posição 51</t>
+  </si>
+  <si>
+    <t>Unidade Posição 52</t>
+  </si>
+  <si>
+    <t>Unidade Posição 53</t>
+  </si>
+  <si>
+    <t>Unidade Posição 54</t>
+  </si>
+  <si>
+    <t>Unidade Posição 55</t>
   </si>
 </sst>
 </file>
@@ -542,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -564,7 +567,7 @@
         <v>105</v>
       </c>
       <c r="C2">
-        <v>36686</v>
+        <v>36791</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -594,10 +597,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>99893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -616,10 +619,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>45961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -627,7 +630,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -638,10 +641,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>41366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -660,10 +663,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -671,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>4486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -693,10 +696,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>615767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -715,10 +718,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -737,10 +740,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -748,10 +751,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>14998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -759,10 +762,10 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -781,10 +784,10 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>26506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -825,10 +828,10 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>837869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -836,10 +839,10 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -880,10 +883,10 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>14631</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -891,10 +894,10 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -913,10 +916,10 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>71950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -946,10 +949,10 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -957,10 +960,10 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -979,10 +982,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>2706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -990,10 +993,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1001,10 +1004,10 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1023,10 +1026,10 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>2176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1034,10 +1037,10 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1045,10 +1048,10 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>450124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1067,10 +1070,10 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1122,10 +1125,10 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>37079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1133,10 +1136,10 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1147,6 +1150,17 @@
         <v>0</v>
       </c>
       <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
         <v>0</v>
       </c>
     </row>

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Unidade</t>
   </si>
@@ -31,163 +31,160 @@
     <t>ALMOXARIFADO DA COORDENADORIA DE REGULAÇÃO EM SAÚDE E AVALIAÇÃO - ALMX/SESAP (20.11.52.99)</t>
   </si>
   <si>
-    <t>Unidade Posição 3</t>
-  </si>
-  <si>
-    <t>Unidade Posição 4</t>
-  </si>
-  <si>
-    <t>Unidade Posição 5</t>
-  </si>
-  <si>
-    <t>Unidade Posição 6</t>
-  </si>
-  <si>
-    <t>Unidade Posição 7</t>
-  </si>
-  <si>
-    <t>Unidade Posição 8</t>
-  </si>
-  <si>
-    <t>Unidade Posição 9</t>
-  </si>
-  <si>
-    <t>Unidade Posição 10</t>
-  </si>
-  <si>
-    <t>Unidade Posição 11</t>
-  </si>
-  <si>
-    <t>Unidade Posição 12</t>
-  </si>
-  <si>
-    <t>Unidade Posição 13</t>
-  </si>
-  <si>
-    <t>Unidade Posição 14</t>
-  </si>
-  <si>
-    <t>Unidade Posição 15</t>
-  </si>
-  <si>
-    <t>Unidade Posição 16</t>
-  </si>
-  <si>
-    <t>Unidade Posição 17</t>
-  </si>
-  <si>
-    <t>Unidade Posição 18</t>
-  </si>
-  <si>
-    <t>Unidade Posição 19</t>
-  </si>
-  <si>
-    <t>Unidade Posição 20</t>
-  </si>
-  <si>
-    <t>Unidade Posição 21</t>
-  </si>
-  <si>
-    <t>Unidade Posição 22</t>
-  </si>
-  <si>
-    <t>Unidade Posição 23</t>
-  </si>
-  <si>
-    <t>Unidade Posição 24</t>
-  </si>
-  <si>
-    <t>Unidade Posição 25</t>
-  </si>
-  <si>
-    <t>Unidade Posição 26</t>
-  </si>
-  <si>
-    <t>Unidade Posição 27</t>
-  </si>
-  <si>
-    <t>Unidade Posição 28</t>
-  </si>
-  <si>
-    <t>Unidade Posição 29</t>
-  </si>
-  <si>
-    <t>Unidade Posição 30</t>
-  </si>
-  <si>
-    <t>Unidade Posição 31</t>
-  </si>
-  <si>
-    <t>Unidade Posição 32</t>
-  </si>
-  <si>
-    <t>Unidade Posição 33</t>
-  </si>
-  <si>
-    <t>Unidade Posição 34</t>
-  </si>
-  <si>
-    <t>Unidade Posição 35</t>
-  </si>
-  <si>
-    <t>Unidade Posição 36</t>
-  </si>
-  <si>
-    <t>Unidade Posição 37</t>
-  </si>
-  <si>
-    <t>Unidade Posição 38</t>
-  </si>
-  <si>
-    <t>Unidade Posição 39</t>
-  </si>
-  <si>
-    <t>Unidade Posição 40</t>
-  </si>
-  <si>
-    <t>Unidade Posição 41</t>
-  </si>
-  <si>
-    <t>Unidade Posição 42</t>
-  </si>
-  <si>
-    <t>Unidade Posição 43</t>
-  </si>
-  <si>
-    <t>Unidade Posição 44</t>
-  </si>
-  <si>
-    <t>Unidade Posição 45</t>
-  </si>
-  <si>
-    <t>Unidade Posição 46</t>
-  </si>
-  <si>
-    <t>Unidade Posição 47</t>
-  </si>
-  <si>
-    <t>Unidade Posição 48</t>
-  </si>
-  <si>
-    <t>Unidade Posição 49</t>
-  </si>
-  <si>
-    <t>Unidade Posição 50</t>
-  </si>
-  <si>
-    <t>Unidade Posição 51</t>
-  </si>
-  <si>
-    <t>Unidade Posição 52</t>
-  </si>
-  <si>
-    <t>Unidade Posição 53</t>
-  </si>
-  <si>
-    <t>Unidade Posição 54</t>
-  </si>
-  <si>
-    <t>Unidade Posição 55</t>
+    <t>ALMOXARIFADO DO CENTRO ESTADUAL DE REABILITAÇÃO E ATENÇÃO AMBULATORIAL ESPECIALIZADA - ALMX/CERAE/SES (20.00.25.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO CERAE (20.00.25.10)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HEMOCENTRO DE CAICÓ (20.00.27.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO COLETA E TRANSFUSÃO DO HEMOCENTRO DE PAU DOS FERROS - ALMX/CT/HEM/PF (20.00.30.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HEMOCENTRO DALTON CUNHA - ALMX/HEM/NAT/SESAP (20.00.26.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HEMOCENTRO DALTON CUNHA - ALMX/HEM/NUT/SESAP (20.00.26.40)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HEMOCENTRO DE MOSSORÓ (20.00.28.13)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL AGUINALDO PEREIRA (20.00.16.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL AGUINALDO PEREIRA (20.00.16.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL ALFREDO MESQUITA FILHO - ALMX/HRAMF (20.00.06.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL ALFREDO MESQUITA FILHO - ALMX/NUTHRAMF (20.00.06.98)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL REGIONAL ANTÔNIO BARROS (20.00.08.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL MONSENHOR ANTÔNIO BARROS (20.00.08.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL CLEODON CARLOS DE ANDRADE (20.00.17.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL CLEODON CARLOS DE ANDRADE (20.00.17.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUT/HRDML (20.00.07.11.01.98)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO COMUM - ALMX/HRDML (20.00.07.11.01.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL GISELDA TRIGUEIRO - ALMX/HGT/SESAP (20.00.03.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL GISELDA TRIGUEIRO (20.00.03.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL HÉLIO MORAIS MARINHO (20.00.15.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL HÉLIO MORAIS MARINHO (20.00.15.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL GERAL DOUTOR JOÃO MACHADO (20.00.04.40)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL GERAL DOUTOR JOÃO MACHADO (20.00.04.43)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL JOSEFA ALVES GODEIRO (20.00.10.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL JOSEFA ALVES GODEIRO (20.00.10.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HJPB - ALMX/NUTR/HJPB (20.00.02.98)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO - ALMX/HJPB (20.00.02.01.01.02.01.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL LINDOLFO GOMES VIDAL (20.00.09.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL LINDOLFO GOMES VIDAL (20.00.09.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL MARIA ALICE FERNANDES (20.00.05.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL MARIA ALICE FERNANDES (20.00.05.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO - ALMX/HRMC (20.00.18.12.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUTR/HRMC (20.00.18.11.03.02.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL MONSENHOR EXPEDITO (20.00.11.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL MONSENHOR EXPEDITO (20.00.11.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL DA MULHER PARTEIRA MARIA CORREIA (20.00.45.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL DA MULHER PARTEIRA MARIA CORREIA (20.00.45.03)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL NELSON INÁCIO DOS SANTOS (20.00.12.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL NELSON INÁCIO DOS SANTOS (20.00.12.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL REGIONAL DOUTOR RAFAEL FERNANDES (20.00.14.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL HOSPITAL REGIONAL DOUTOR RAFAEL FERNANDES (20.00.14.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL TARCÍSIO MAIA (20.00.13.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL TARCÍSIO MAIA (20.00.13.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL ESTADUAL TELECILA FREITAS FONTES (20.00.19.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL ESTADUAL TELECILA FREITAS FONTES (20.00.19.02)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO HOSPITAL MONSENHOR WALFREDO GURGEL - ALMX/HMWG (20.00.01.01.04.03.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUT/HMWG (20.00.01.01.05.06.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DO LABORATÓRIO DE CITOPATOLOGIA DE MOSSORÓ (20.99.10.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO DE SUPRIMENTOS DO LACEN - ALMX/LACEN/SES (20.00.20.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO LAREM (20.00.22.01)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO LABORATÓRIO REGIONAL DE CAICÓ DR. JOÃO PAULO FILGUEIRA (20.00.21.03)</t>
+  </si>
+  <si>
+    <t>DIVISÃO DE ALMOXARIFADO - DIVALMX/LAREPF/SESAP (20.00.23.01.01.02)</t>
   </si>
 </sst>
 </file>
@@ -545,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -597,10 +594,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100219</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -619,10 +616,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -630,10 +627,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,10 +638,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>41401</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -663,10 +660,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,10 +671,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -696,10 +693,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>616475</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,10 +715,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -740,10 +737,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -751,10 +748,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>15016</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -762,10 +759,10 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,10 +781,10 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>26548</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -828,10 +825,10 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>838847</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -839,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -883,10 +880,10 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>14683</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,10 +891,10 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -916,10 +913,10 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>72038</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -927,10 +924,10 @@
         <v>36</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -938,10 +935,10 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -949,10 +946,10 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -960,10 +957,10 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -971,7 +968,7 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -982,10 +979,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -993,10 +990,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,10 +1001,10 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1015,7 +1012,7 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1026,10 +1023,10 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1037,10 +1034,10 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1048,10 +1045,10 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>450521</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1059,10 +1056,10 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1070,10 +1067,10 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1125,10 +1122,10 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>37195</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1136,10 +1133,10 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1150,17 +1147,6 @@
         <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
         <v>0</v>
       </c>
     </row>

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -124,10 +124,10 @@
     <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL MARIA ALICE FERNANDES (20.00.05.02)</t>
   </si>
   <si>
-    <t>ALMOXARIFADO - ALMX/HRMC (20.00.18.12.99)</t>
-  </si>
-  <si>
-    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUTR/HRMC (20.00.18.11.03.02.99)</t>
+    <t>ALMOXARIFADO CENTRAL - ALMX/HDMC/CN (20.00.18.12.99)</t>
+  </si>
+  <si>
+    <t>ALMOXARIFADO NUTRICIONAL - ALMX/NUTR/HDMC (20.00.18.11.03.02.99)</t>
   </si>
   <si>
     <t>ALMOXARIFADO NUTRICIONAL DO HOSPITAL REGIONAL MONSENHOR EXPEDITO (20.00.11.02)</t>
@@ -564,7 +564,7 @@
         <v>105</v>
       </c>
       <c r="C2">
-        <v>36791</v>
+        <v>36896</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -597,7 +597,7 @@
         <v>326</v>
       </c>
       <c r="C5">
-        <v>100219</v>
+        <v>100545</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -619,7 +619,7 @@
         <v>153</v>
       </c>
       <c r="C7">
-        <v>46114</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>41401</v>
+        <v>41436</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -663,7 +663,7 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>1370</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4490</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -696,7 +696,7 @@
         <v>708</v>
       </c>
       <c r="C14">
-        <v>616475</v>
+        <v>617183</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -740,7 +740,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -751,7 +751,7 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>15016</v>
+        <v>15034</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -762,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>26548</v>
+        <v>26590</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -828,7 +828,7 @@
         <v>978</v>
       </c>
       <c r="C26">
-        <v>838847</v>
+        <v>839825</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -839,7 +839,7 @@
         <v>19</v>
       </c>
       <c r="C27">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -883,7 +883,7 @@
         <v>52</v>
       </c>
       <c r="C31">
-        <v>14683</v>
+        <v>14735</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -916,7 +916,7 @@
         <v>88</v>
       </c>
       <c r="C34">
-        <v>72038</v>
+        <v>72126</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -927,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -938,7 +938,7 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1909</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -960,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -982,7 +982,7 @@
         <v>90</v>
       </c>
       <c r="C40">
-        <v>2796</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1015,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>2181</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1034,10 +1034,10 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1048,7 +1048,7 @@
         <v>397</v>
       </c>
       <c r="C46">
-        <v>450521</v>
+        <v>450918</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1059,7 +1059,7 @@
         <v>5</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>116</v>
       </c>
       <c r="C53">
-        <v>37195</v>
+        <v>37311</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="C54">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -564,7 +564,7 @@
         <v>105</v>
       </c>
       <c r="C2">
-        <v>36896</v>
+        <v>37001</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -594,10 +594,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C5">
-        <v>100545</v>
+        <v>100872</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -619,7 +619,7 @@
         <v>153</v>
       </c>
       <c r="C7">
-        <v>46267</v>
+        <v>46420</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>41436</v>
+        <v>41471</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -649,7 +649,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>1399</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4494</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -696,7 +696,7 @@
         <v>708</v>
       </c>
       <c r="C14">
-        <v>617183</v>
+        <v>617891</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>291</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -737,10 +737,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -748,10 +748,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19">
-        <v>15034</v>
+        <v>15053</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -762,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>26590</v>
+        <v>26632</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -825,10 +825,10 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C26">
-        <v>839825</v>
+        <v>840803</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -839,7 +839,7 @@
         <v>19</v>
       </c>
       <c r="C27">
-        <v>314</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -869,7 +869,7 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>52</v>
       </c>
       <c r="C31">
-        <v>14735</v>
+        <v>14787</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -902,7 +902,7 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>88</v>
       </c>
       <c r="C34">
-        <v>72126</v>
+        <v>72214</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -924,10 +924,10 @@
         <v>36</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -938,7 +938,7 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1913</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -960,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -968,10 +968,10 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -979,10 +979,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C40">
-        <v>2886</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1012,10 +1012,10 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>2187</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1048,7 +1048,7 @@
         <v>397</v>
       </c>
       <c r="C46">
-        <v>450918</v>
+        <v>451315</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1056,10 +1056,10 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>116</v>
       </c>
       <c r="C53">
-        <v>37311</v>
+        <v>37427</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="C54">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -564,7 +564,7 @@
         <v>105</v>
       </c>
       <c r="C2">
-        <v>37001</v>
+        <v>37316</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -597,7 +597,7 @@
         <v>327</v>
       </c>
       <c r="C5">
-        <v>100872</v>
+        <v>101853</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -619,7 +619,7 @@
         <v>153</v>
       </c>
       <c r="C7">
-        <v>46420</v>
+        <v>46879</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>41471</v>
+        <v>41576</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -652,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -663,7 +663,7 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>1428</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4498</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -693,10 +693,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C14">
-        <v>617891</v>
+        <v>620018</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>307</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -751,7 +751,7 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>15053</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -762,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>26632</v>
+        <v>26758</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -828,7 +828,7 @@
         <v>979</v>
       </c>
       <c r="C26">
-        <v>840803</v>
+        <v>843740</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -839,7 +839,7 @@
         <v>19</v>
       </c>
       <c r="C27">
-        <v>333</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -869,7 +869,7 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>52</v>
       </c>
       <c r="C31">
-        <v>14787</v>
+        <v>14943</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>180</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -905,7 +905,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -916,7 +916,7 @@
         <v>88</v>
       </c>
       <c r="C34">
-        <v>72214</v>
+        <v>72478</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -935,10 +935,10 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1917</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -960,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -982,7 +982,7 @@
         <v>102</v>
       </c>
       <c r="C40">
-        <v>2981</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>2193</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1048,7 +1048,7 @@
         <v>397</v>
       </c>
       <c r="C46">
-        <v>451315</v>
+        <v>452506</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>116</v>
       </c>
       <c r="C53">
-        <v>37427</v>
+        <v>37775</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="C54">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -649,10 +649,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -836,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1122,7 +1122,7 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C53">
         <v>37775</v>
@@ -1133,7 +1133,7 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C54">
         <v>28</v>

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -561,10 +561,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C2">
-        <v>37316</v>
+        <v>37421</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -594,10 +594,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C5">
-        <v>101853</v>
+        <v>102180</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -619,7 +619,7 @@
         <v>153</v>
       </c>
       <c r="C7">
-        <v>46879</v>
+        <v>47032</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>41576</v>
+        <v>41611</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -652,7 +652,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -663,7 +663,7 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>1515</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4510</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -696,7 +696,7 @@
         <v>709</v>
       </c>
       <c r="C14">
-        <v>620018</v>
+        <v>620727</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>355</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -751,7 +751,7 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>15110</v>
+        <v>15129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -762,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>26758</v>
+        <v>26800</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -825,10 +825,10 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C26">
-        <v>843740</v>
+        <v>844719</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -883,7 +883,7 @@
         <v>52</v>
       </c>
       <c r="C31">
-        <v>14943</v>
+        <v>14995</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -905,7 +905,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -916,7 +916,7 @@
         <v>88</v>
       </c>
       <c r="C34">
-        <v>72478</v>
+        <v>72566</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1929</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -960,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -979,10 +979,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C40">
-        <v>3287</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>2211</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1048,7 +1048,7 @@
         <v>397</v>
       </c>
       <c r="C46">
-        <v>452506</v>
+        <v>452903</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>118</v>
       </c>
       <c r="C53">
-        <v>37775</v>
+        <v>37893</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1136,7 +1136,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/Base_Indicador_Atrasos.xlsx
+++ b/Base_Indicador_Atrasos.xlsx
@@ -564,7 +564,7 @@
         <v>110</v>
       </c>
       <c r="C2">
-        <v>37421</v>
+        <v>37531</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -594,10 +594,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5">
-        <v>102180</v>
+        <v>102511</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -619,7 +619,7 @@
         <v>153</v>
       </c>
       <c r="C7">
-        <v>47032</v>
+        <v>47185</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -641,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>41611</v>
+        <v>41646</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -649,10 +649,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -663,7 +663,7 @@
         <v>29</v>
       </c>
       <c r="C11">
-        <v>1544</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4514</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -696,7 +696,7 @@
         <v>709</v>
       </c>
       <c r="C14">
-        <v>620727</v>
+        <v>621436</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>371</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -751,7 +751,7 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>15129</v>
+        <v>15148</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -759,10 +759,10 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -784,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>26800</v>
+        <v>26842</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -828,7 +828,7 @@
         <v>980</v>
       </c>
       <c r="C26">
-        <v>844719</v>
+        <v>845699</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -883,7 +883,7 @@
         <v>52</v>
       </c>
       <c r="C31">
-        <v>14995</v>
+        <v>15047</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -894,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -902,10 +902,10 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -916,7 +916,7 @@
         <v>88</v>
       </c>
       <c r="C34">
-        <v>72566</v>
+        <v>72654</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>1933</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -957,10 +957,10 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -982,7 +982,7 @@
         <v>105</v>
       </c>
       <c r="C40">
-        <v>3392</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -990,10 +990,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>2217</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1048,7 +1048,7 @@
         <v>397</v>
       </c>
       <c r="C46">
-        <v>452903</v>
+        <v>453300</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1111,10 +1111,10 @@
         <v>53</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>118</v>
       </c>
       <c r="C53">
-        <v>37893</v>
+        <v>38011</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1133,10 +1133,10 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:3">
